--- a/Results_censored.xlsx
+++ b/Results_censored.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3bb354d7fb258327/Masterarbeit - LLMs in VAT - Knogler Lukas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Users\Lukas\Documents\GitHub\ct-solver-results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{CE06DAB6-75C9-452E-AEA8-CC75F7CDA0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CC7A9AE-951A-4076-BC70-CAB57D54FEB0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE27629-1B27-40CA-886D-20172E83DB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{C33311FD-58FD-4CDF-835E-5DE7D1C349B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C33311FD-58FD-4CDF-835E-5DE7D1C349B6}"/>
   </bookViews>
   <sheets>
     <sheet name="total data" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -11924,207 +11924,6 @@
     <t>{"text": "see original source, M&amp;W chapter 3-5-2 page 174"}</t>
   </si>
   <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 1"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 2"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 3"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 4"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 4a"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 5"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 6"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 7"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 8"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 9"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 10"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 11"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 12"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 13"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 14"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 15"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 16"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 17"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 17a"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 18"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 19"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 20"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 20a"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 21"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 22"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 23"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 24"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 25"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 26"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 27"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 28"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 29"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 30"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 31"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 32"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 33"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 34"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 35"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 36"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 39"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 40"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 41"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 42"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 43"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 44"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 45"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 46"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 47"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 48"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 49"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 50"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 51"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 52"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 53"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 54"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 55"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 56"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 57"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 58"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 59"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 60"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 61"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 62"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 63"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 64"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 65"}</t>
-  </si>
-  <si>
-    <t>{"text": "see original source, Dupont 2012  Beispiel 66"}</t>
-  </si>
-  <si>
     <t>{"text": "see original source, KOLLMANN Beispiel 1"}</t>
   </si>
   <si>
@@ -12210,6 +12009,207 @@
   </si>
   <si>
     <t>9819cbf4-fbbc-4788-833d-0af03673a16b</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 1"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 2"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 3"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 4"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 4a"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 5"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 6"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 7"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 8"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 9"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 10"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 11"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 12"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 13"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 14"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 15"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 16"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 17"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 17a"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 18"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 19"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 20"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 20a"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 21"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 22"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 23"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 24"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 25"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 26"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 27"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 28"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 29"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 30"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 31"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 32"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 33"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 34"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 35"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 36"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 39"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 40"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 41"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 42"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 43"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 44"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 45"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 46"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 47"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 48"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 49"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 50"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 51"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 52"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 53"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 54"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 55"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 56"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 57"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 58"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 59"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 60"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 61"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 62"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 63"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 64"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 65"}</t>
+  </si>
+  <si>
+    <t>{"text": "see original source, Dupont  Beispiel 66"}</t>
   </si>
 </sst>
 </file>
@@ -17378,7 +17378,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E787C249-8635-4346-8BC1-6E35D26D30D9}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E787C249-8635-4346-8BC1-6E35D26D30D9}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sets">
   <location ref="A1:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
@@ -17551,7 +17551,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B112B754-5FEB-4FF5-B39B-DA19EEB0CE25}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sample sets">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B112B754-5FEB-4FF5-B39B-DA19EEB0CE25}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sample sets">
   <location ref="A1:E6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
@@ -18111,7 +18111,7 @@
         <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>1383</v>
+        <v>1316</v>
       </c>
       <c r="D2" t="s">
         <v>495</v>
@@ -22752,7 +22752,7 @@
         <v>269</v>
       </c>
       <c r="C74" t="s">
-        <v>1296</v>
+        <v>1325</v>
       </c>
       <c r="D74" t="s">
         <v>695</v>
@@ -22770,7 +22770,7 @@
         <v>6.1180000000000002E-3</v>
       </c>
       <c r="J74" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K74" t="s">
         <v>72</v>
@@ -22817,7 +22817,7 @@
         <v>275</v>
       </c>
       <c r="C75" t="s">
-        <v>1297</v>
+        <v>1326</v>
       </c>
       <c r="D75" t="s">
         <v>675</v>
@@ -22835,7 +22835,7 @@
         <v>6.3740000000000003E-3</v>
       </c>
       <c r="J75" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K75" t="s">
         <v>73</v>
@@ -22882,7 +22882,7 @@
         <v>251</v>
       </c>
       <c r="C76" t="s">
-        <v>1298</v>
+        <v>1327</v>
       </c>
       <c r="D76" t="s">
         <v>737</v>
@@ -22900,7 +22900,7 @@
         <v>6.2560000000000003E-3</v>
       </c>
       <c r="J76" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K76" t="s">
         <v>74</v>
@@ -22947,7 +22947,7 @@
         <v>265</v>
       </c>
       <c r="C77" t="s">
-        <v>1299</v>
+        <v>1328</v>
       </c>
       <c r="D77" t="s">
         <v>704</v>
@@ -22965,7 +22965,7 @@
         <v>6.1739999999999998E-3</v>
       </c>
       <c r="J77" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K77" t="s">
         <v>75</v>
@@ -23012,7 +23012,7 @@
         <v>281</v>
       </c>
       <c r="C78" t="s">
-        <v>1300</v>
+        <v>1329</v>
       </c>
       <c r="D78" t="s">
         <v>659</v>
@@ -23030,7 +23030,7 @@
         <v>6.1999999999999998E-3</v>
       </c>
       <c r="J78" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K78" t="s">
         <v>94</v>
@@ -23077,7 +23077,7 @@
         <v>302</v>
       </c>
       <c r="C79" t="s">
-        <v>1301</v>
+        <v>1330</v>
       </c>
       <c r="D79" t="s">
         <v>613</v>
@@ -23095,7 +23095,7 @@
         <v>6.2599999999999999E-3</v>
       </c>
       <c r="J79" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K79" t="s">
         <v>76</v>
@@ -23142,7 +23142,7 @@
         <v>291</v>
       </c>
       <c r="C80" t="s">
-        <v>1302</v>
+        <v>1331</v>
       </c>
       <c r="D80" t="s">
         <v>638</v>
@@ -23160,7 +23160,7 @@
         <v>6.2199999999999998E-3</v>
       </c>
       <c r="J80" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K80" t="s">
         <v>77</v>
@@ -23204,7 +23204,7 @@
         <v>282</v>
       </c>
       <c r="C81" t="s">
-        <v>1303</v>
+        <v>1332</v>
       </c>
       <c r="D81" t="s">
         <v>657</v>
@@ -23222,7 +23222,7 @@
         <v>6.3220000000000004E-3</v>
       </c>
       <c r="J81" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K81" t="s">
         <v>78</v>
@@ -23269,7 +23269,7 @@
         <v>297</v>
       </c>
       <c r="C82" t="s">
-        <v>1304</v>
+        <v>1333</v>
       </c>
       <c r="D82" t="s">
         <v>624</v>
@@ -23287,7 +23287,7 @@
         <v>5.5579999999999996E-3</v>
       </c>
       <c r="J82" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K82" t="s">
         <v>79</v>
@@ -23334,7 +23334,7 @@
         <v>256</v>
       </c>
       <c r="C83" t="s">
-        <v>1305</v>
+        <v>1334</v>
       </c>
       <c r="D83" t="s">
         <v>725</v>
@@ -23352,7 +23352,7 @@
         <v>5.9100000000000003E-3</v>
       </c>
       <c r="J83" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K83" t="s">
         <v>80</v>
@@ -23399,7 +23399,7 @@
         <v>355</v>
       </c>
       <c r="C84" t="s">
-        <v>1306</v>
+        <v>1335</v>
       </c>
       <c r="D84" t="s">
         <v>692</v>
@@ -23417,7 +23417,7 @@
         <v>6.9259999999999999E-3</v>
       </c>
       <c r="J84" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K84" t="s">
         <v>81</v>
@@ -23464,7 +23464,7 @@
         <v>354</v>
       </c>
       <c r="C85" t="s">
-        <v>1307</v>
+        <v>1336</v>
       </c>
       <c r="D85" t="s">
         <v>649</v>
@@ -23482,7 +23482,7 @@
         <v>6.2199999999999998E-3</v>
       </c>
       <c r="J85" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K85" t="s">
         <v>82</v>
@@ -23529,7 +23529,7 @@
         <v>259</v>
       </c>
       <c r="C86" t="s">
-        <v>1308</v>
+        <v>1337</v>
       </c>
       <c r="D86" t="s">
         <v>720</v>
@@ -23547,7 +23547,7 @@
         <v>6.862E-3</v>
       </c>
       <c r="J86" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K86" t="s">
         <v>83</v>
@@ -23594,7 +23594,7 @@
         <v>270</v>
       </c>
       <c r="C87" t="s">
-        <v>1309</v>
+        <v>1338</v>
       </c>
       <c r="D87" t="s">
         <v>690</v>
@@ -23612,7 +23612,7 @@
         <v>6.4739999999999997E-3</v>
       </c>
       <c r="J87" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K87" t="s">
         <v>84</v>
@@ -23659,7 +23659,7 @@
         <v>299</v>
       </c>
       <c r="C88" t="s">
-        <v>1310</v>
+        <v>1339</v>
       </c>
       <c r="D88" t="s">
         <v>620</v>
@@ -23677,7 +23677,7 @@
         <v>6.6179999999999998E-3</v>
       </c>
       <c r="J88" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K88" t="s">
         <v>85</v>
@@ -23721,10 +23721,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>1391</v>
+        <v>1324</v>
       </c>
       <c r="C89" t="s">
-        <v>1311</v>
+        <v>1340</v>
       </c>
       <c r="D89" t="s">
         <v>708</v>
@@ -23742,7 +23742,7 @@
         <v>6.3920000000000001E-3</v>
       </c>
       <c r="J89" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K89" t="s">
         <v>86</v>
@@ -23789,7 +23789,7 @@
         <v>279</v>
       </c>
       <c r="C90" t="s">
-        <v>1312</v>
+        <v>1341</v>
       </c>
       <c r="D90" t="s">
         <v>663</v>
@@ -23807,7 +23807,7 @@
         <v>6.4159999999999998E-3</v>
       </c>
       <c r="J90" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K90" t="s">
         <v>87</v>
@@ -23854,7 +23854,7 @@
         <v>268</v>
       </c>
       <c r="C91" t="s">
-        <v>1313</v>
+        <v>1342</v>
       </c>
       <c r="D91" t="s">
         <v>697</v>
@@ -23872,7 +23872,7 @@
         <v>7.5719999999999997E-3</v>
       </c>
       <c r="J91" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K91" t="s">
         <v>88</v>
@@ -23919,7 +23919,7 @@
         <v>459</v>
       </c>
       <c r="C92" t="s">
-        <v>1314</v>
+        <v>1343</v>
       </c>
       <c r="D92" t="s">
         <v>731</v>
@@ -23937,7 +23937,7 @@
         <v>7.0520000000000001E-3</v>
       </c>
       <c r="J92" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K92" t="s">
         <v>95</v>
@@ -23984,7 +23984,7 @@
         <v>300</v>
       </c>
       <c r="C93" t="s">
-        <v>1315</v>
+        <v>1344</v>
       </c>
       <c r="D93" t="s">
         <v>618</v>
@@ -24002,7 +24002,7 @@
         <v>5.672E-3</v>
       </c>
       <c r="J93" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K93" t="s">
         <v>89</v>
@@ -24049,7 +24049,7 @@
         <v>263</v>
       </c>
       <c r="C94" t="s">
-        <v>1316</v>
+        <v>1345</v>
       </c>
       <c r="D94" t="s">
         <v>712</v>
@@ -24067,7 +24067,7 @@
         <v>6.0959999999999999E-3</v>
       </c>
       <c r="J94" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K94" t="s">
         <v>90</v>
@@ -24114,7 +24114,7 @@
         <v>288</v>
       </c>
       <c r="C95" t="s">
-        <v>1317</v>
+        <v>1346</v>
       </c>
       <c r="D95" t="s">
         <v>643</v>
@@ -24132,7 +24132,7 @@
         <v>6.1180000000000002E-3</v>
       </c>
       <c r="J95" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K95" t="s">
         <v>91</v>
@@ -24179,7 +24179,7 @@
         <v>273</v>
       </c>
       <c r="C96" t="s">
-        <v>1318</v>
+        <v>1347</v>
       </c>
       <c r="D96" t="s">
         <v>682</v>
@@ -24197,7 +24197,7 @@
         <v>6.1900000000000002E-3</v>
       </c>
       <c r="J96" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K96" t="s">
         <v>100</v>
@@ -24244,7 +24244,7 @@
         <v>295</v>
       </c>
       <c r="C97" t="s">
-        <v>1319</v>
+        <v>1348</v>
       </c>
       <c r="D97" t="s">
         <v>628</v>
@@ -24262,7 +24262,7 @@
         <v>6.5640000000000004E-3</v>
       </c>
       <c r="J97" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K97" t="s">
         <v>92</v>
@@ -24309,7 +24309,7 @@
         <v>271</v>
       </c>
       <c r="C98" t="s">
-        <v>1320</v>
+        <v>1349</v>
       </c>
       <c r="D98" t="s">
         <v>686</v>
@@ -24327,7 +24327,7 @@
         <v>6.0740000000000004E-3</v>
       </c>
       <c r="J98" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K98" t="s">
         <v>93</v>
@@ -24374,7 +24374,7 @@
         <v>283</v>
       </c>
       <c r="C99" t="s">
-        <v>1321</v>
+        <v>1350</v>
       </c>
       <c r="D99" t="s">
         <v>654</v>
@@ -24392,7 +24392,7 @@
         <v>6.1260000000000004E-3</v>
       </c>
       <c r="J99" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K99" t="s">
         <v>96</v>
@@ -24439,7 +24439,7 @@
         <v>301</v>
       </c>
       <c r="C100" t="s">
-        <v>1322</v>
+        <v>1351</v>
       </c>
       <c r="D100" t="s">
         <v>616</v>
@@ -24457,7 +24457,7 @@
         <v>6.6499999999999997E-3</v>
       </c>
       <c r="J100" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K100" t="s">
         <v>97</v>
@@ -24504,7 +24504,7 @@
         <v>266</v>
       </c>
       <c r="C101" t="s">
-        <v>1323</v>
+        <v>1352</v>
       </c>
       <c r="D101" t="s">
         <v>703</v>
@@ -24522,7 +24522,7 @@
         <v>7.2719999999999998E-3</v>
       </c>
       <c r="J101" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K101" t="s">
         <v>98</v>
@@ -24566,7 +24566,7 @@
         <v>289</v>
       </c>
       <c r="C102" t="s">
-        <v>1324</v>
+        <v>1353</v>
       </c>
       <c r="D102" t="s">
         <v>641</v>
@@ -24584,7 +24584,7 @@
         <v>6.8459999999999997E-3</v>
       </c>
       <c r="J102" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K102" t="s">
         <v>99</v>
@@ -24631,7 +24631,7 @@
         <v>274</v>
       </c>
       <c r="C103" t="s">
-        <v>1325</v>
+        <v>1354</v>
       </c>
       <c r="D103" t="s">
         <v>679</v>
@@ -24649,7 +24649,7 @@
         <v>6.7920000000000003E-3</v>
       </c>
       <c r="J103" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K103" t="s">
         <v>101</v>
@@ -24696,7 +24696,7 @@
         <v>293</v>
       </c>
       <c r="C104" t="s">
-        <v>1326</v>
+        <v>1355</v>
       </c>
       <c r="D104" t="s">
         <v>634</v>
@@ -24714,7 +24714,7 @@
         <v>7.7279999999999996E-3</v>
       </c>
       <c r="J104" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K104" t="s">
         <v>102</v>
@@ -24761,7 +24761,7 @@
         <v>243</v>
       </c>
       <c r="C105" t="s">
-        <v>1327</v>
+        <v>1356</v>
       </c>
       <c r="D105" t="s">
         <v>677</v>
@@ -24779,7 +24779,7 @@
         <v>6.0480000000000004E-3</v>
       </c>
       <c r="J105" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K105" t="s">
         <v>103</v>
@@ -24826,7 +24826,7 @@
         <v>244</v>
       </c>
       <c r="C106" t="s">
-        <v>1328</v>
+        <v>1357</v>
       </c>
       <c r="D106" t="s">
         <v>694</v>
@@ -24844,7 +24844,7 @@
         <v>6.182E-3</v>
       </c>
       <c r="J106" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K106" t="s">
         <v>104</v>
@@ -24888,7 +24888,7 @@
         <v>245</v>
       </c>
       <c r="C107" t="s">
-        <v>1329</v>
+        <v>1358</v>
       </c>
       <c r="D107" t="s">
         <v>688</v>
@@ -24906,7 +24906,7 @@
         <v>5.8199999999999997E-3</v>
       </c>
       <c r="J107" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K107" t="s">
         <v>105</v>
@@ -24953,7 +24953,7 @@
         <v>250</v>
       </c>
       <c r="C108" t="s">
-        <v>1330</v>
+        <v>1359</v>
       </c>
       <c r="D108" t="s">
         <v>739</v>
@@ -24971,7 +24971,7 @@
         <v>5.738E-3</v>
       </c>
       <c r="J108" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K108" t="s">
         <v>106</v>
@@ -25018,7 +25018,7 @@
         <v>264</v>
       </c>
       <c r="C109" t="s">
-        <v>1331</v>
+        <v>1360</v>
       </c>
       <c r="D109" t="s">
         <v>710</v>
@@ -25036,7 +25036,7 @@
         <v>5.5840000000000004E-3</v>
       </c>
       <c r="J109" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K109" t="s">
         <v>107</v>
@@ -25083,7 +25083,7 @@
         <v>246</v>
       </c>
       <c r="C110" t="s">
-        <v>1332</v>
+        <v>1361</v>
       </c>
       <c r="D110" t="s">
         <v>699</v>
@@ -25101,7 +25101,7 @@
         <v>5.9880000000000003E-3</v>
       </c>
       <c r="J110" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K110" t="s">
         <v>108</v>
@@ -25148,7 +25148,7 @@
         <v>247</v>
       </c>
       <c r="C111" t="s">
-        <v>1333</v>
+        <v>1362</v>
       </c>
       <c r="D111" t="s">
         <v>671</v>
@@ -25166,7 +25166,7 @@
         <v>6.5659999999999998E-3</v>
       </c>
       <c r="J111" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K111" t="s">
         <v>109</v>
@@ -25213,7 +25213,7 @@
         <v>242</v>
       </c>
       <c r="C112" t="s">
-        <v>1334</v>
+        <v>1363</v>
       </c>
       <c r="D112" t="s">
         <v>630</v>
@@ -25231,7 +25231,7 @@
         <v>6.0280000000000004E-3</v>
       </c>
       <c r="J112" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K112" t="s">
         <v>110</v>
@@ -25278,7 +25278,7 @@
         <v>287</v>
       </c>
       <c r="C113" t="s">
-        <v>1335</v>
+        <v>1364</v>
       </c>
       <c r="D113" t="s">
         <v>645</v>
@@ -25296,7 +25296,7 @@
         <v>6.5319999999999996E-3</v>
       </c>
       <c r="J113" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K113" t="s">
         <v>111</v>
@@ -25343,7 +25343,7 @@
         <v>267</v>
       </c>
       <c r="C114" t="s">
-        <v>1336</v>
+        <v>1365</v>
       </c>
       <c r="D114" t="s">
         <v>701</v>
@@ -25361,7 +25361,7 @@
         <v>5.6179999999999997E-3</v>
       </c>
       <c r="J114" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K114" t="s">
         <v>112</v>
@@ -25408,7 +25408,7 @@
         <v>298</v>
       </c>
       <c r="C115" t="s">
-        <v>1337</v>
+        <v>1366</v>
       </c>
       <c r="D115" t="s">
         <v>622</v>
@@ -25426,7 +25426,7 @@
         <v>6.7060000000000002E-3</v>
       </c>
       <c r="J115" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K115" t="s">
         <v>113</v>
@@ -25473,7 +25473,7 @@
         <v>280</v>
       </c>
       <c r="C116" t="s">
-        <v>1338</v>
+        <v>1367</v>
       </c>
       <c r="D116" t="s">
         <v>661</v>
@@ -25491,7 +25491,7 @@
         <v>5.9080000000000001E-3</v>
       </c>
       <c r="J116" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K116" t="s">
         <v>114</v>
@@ -25538,7 +25538,7 @@
         <v>252</v>
       </c>
       <c r="C117" t="s">
-        <v>1339</v>
+        <v>1368</v>
       </c>
       <c r="D117" t="s">
         <v>735</v>
@@ -25556,7 +25556,7 @@
         <v>5.666E-3</v>
       </c>
       <c r="J117" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K117" t="s">
         <v>115</v>
@@ -25603,7 +25603,7 @@
         <v>257</v>
       </c>
       <c r="C118" t="s">
-        <v>1340</v>
+        <v>1369</v>
       </c>
       <c r="D118" t="s">
         <v>723</v>
@@ -25621,7 +25621,7 @@
         <v>6.3800000000000003E-3</v>
       </c>
       <c r="J118" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K118" t="s">
         <v>116</v>
@@ -25668,7 +25668,7 @@
         <v>260</v>
       </c>
       <c r="C119" t="s">
-        <v>1341</v>
+        <v>1370</v>
       </c>
       <c r="D119" t="s">
         <v>718</v>
@@ -25686,7 +25686,7 @@
         <v>6.3720000000000001E-3</v>
       </c>
       <c r="J119" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K119" t="s">
         <v>117</v>
@@ -25733,7 +25733,7 @@
         <v>258</v>
       </c>
       <c r="C120" t="s">
-        <v>1342</v>
+        <v>1371</v>
       </c>
       <c r="D120" t="s">
         <v>722</v>
@@ -25751,7 +25751,7 @@
         <v>6.3579999999999999E-3</v>
       </c>
       <c r="J120" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K120" t="s">
         <v>118</v>
@@ -25795,7 +25795,7 @@
         <v>254</v>
       </c>
       <c r="C121" t="s">
-        <v>1343</v>
+        <v>1372</v>
       </c>
       <c r="D121" t="s">
         <v>729</v>
@@ -25813,7 +25813,7 @@
         <v>6.7580000000000001E-3</v>
       </c>
       <c r="J121" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K121" t="s">
         <v>119</v>
@@ -25860,7 +25860,7 @@
         <v>248</v>
       </c>
       <c r="C122" t="s">
-        <v>1344</v>
+        <v>1373</v>
       </c>
       <c r="D122" t="s">
         <v>743</v>
@@ -25878,7 +25878,7 @@
         <v>6.7260000000000002E-3</v>
       </c>
       <c r="J122" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K122" t="s">
         <v>120</v>
@@ -25925,7 +25925,7 @@
         <v>285</v>
       </c>
       <c r="C123" t="s">
-        <v>1345</v>
+        <v>1374</v>
       </c>
       <c r="D123" t="s">
         <v>650</v>
@@ -25943,7 +25943,7 @@
         <v>6.816E-3</v>
       </c>
       <c r="J123" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K123" t="s">
         <v>121</v>
@@ -25990,7 +25990,7 @@
         <v>292</v>
       </c>
       <c r="C124" t="s">
-        <v>1346</v>
+        <v>1375</v>
       </c>
       <c r="D124" t="s">
         <v>636</v>
@@ -26008,7 +26008,7 @@
         <v>6.9719999999999999E-3</v>
       </c>
       <c r="J124" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K124" t="s">
         <v>122</v>
@@ -26055,7 +26055,7 @@
         <v>286</v>
       </c>
       <c r="C125" t="s">
-        <v>1347</v>
+        <v>1376</v>
       </c>
       <c r="D125" t="s">
         <v>647</v>
@@ -26073,7 +26073,7 @@
         <v>7.1739999999999998E-3</v>
       </c>
       <c r="J125" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K125" t="s">
         <v>123</v>
@@ -26120,7 +26120,7 @@
         <v>290</v>
       </c>
       <c r="C126" t="s">
-        <v>1348</v>
+        <v>1377</v>
       </c>
       <c r="D126" t="s">
         <v>639</v>
@@ -26138,7 +26138,7 @@
         <v>6.7460000000000003E-3</v>
       </c>
       <c r="J126" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K126" t="s">
         <v>124</v>
@@ -26185,7 +26185,7 @@
         <v>249</v>
       </c>
       <c r="C127" t="s">
-        <v>1349</v>
+        <v>1378</v>
       </c>
       <c r="D127" t="s">
         <v>741</v>
@@ -26203,7 +26203,7 @@
         <v>7.2760000000000003E-3</v>
       </c>
       <c r="J127" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K127" t="s">
         <v>125</v>
@@ -26250,7 +26250,7 @@
         <v>253</v>
       </c>
       <c r="C128" t="s">
-        <v>1350</v>
+        <v>1379</v>
       </c>
       <c r="D128" t="s">
         <v>733</v>
@@ -26268,7 +26268,7 @@
         <v>6.0340000000000003E-3</v>
       </c>
       <c r="J128" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K128" t="s">
         <v>126</v>
@@ -26315,7 +26315,7 @@
         <v>277</v>
       </c>
       <c r="C129" t="s">
-        <v>1351</v>
+        <v>1380</v>
       </c>
       <c r="D129" t="s">
         <v>668</v>
@@ -26333,7 +26333,7 @@
         <v>6.3680000000000004E-3</v>
       </c>
       <c r="J129" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K129" t="s">
         <v>127</v>
@@ -26380,7 +26380,7 @@
         <v>261</v>
       </c>
       <c r="C130" t="s">
-        <v>1352</v>
+        <v>1381</v>
       </c>
       <c r="D130" t="s">
         <v>716</v>
@@ -26398,7 +26398,7 @@
         <v>5.7499999999999999E-3</v>
       </c>
       <c r="J130" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K130" t="s">
         <v>128</v>
@@ -26445,7 +26445,7 @@
         <v>278</v>
       </c>
       <c r="C131" t="s">
-        <v>1353</v>
+        <v>1382</v>
       </c>
       <c r="D131" t="s">
         <v>665</v>
@@ -26463,7 +26463,7 @@
         <v>5.6340000000000001E-3</v>
       </c>
       <c r="J131" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K131" t="s">
         <v>129</v>
@@ -26510,7 +26510,7 @@
         <v>241</v>
       </c>
       <c r="C132" t="s">
-        <v>1354</v>
+        <v>1383</v>
       </c>
       <c r="D132" t="s">
         <v>745</v>
@@ -26528,7 +26528,7 @@
         <v>5.9119999999999997E-3</v>
       </c>
       <c r="J132" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K132" t="s">
         <v>130</v>
@@ -26575,7 +26575,7 @@
         <v>294</v>
       </c>
       <c r="C133" t="s">
-        <v>1355</v>
+        <v>1384</v>
       </c>
       <c r="D133" t="s">
         <v>632</v>
@@ -26593,7 +26593,7 @@
         <v>5.5399999999999998E-3</v>
       </c>
       <c r="J133" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K133" t="s">
         <v>131</v>
@@ -26640,7 +26640,7 @@
         <v>255</v>
       </c>
       <c r="C134" t="s">
-        <v>1356</v>
+        <v>1385</v>
       </c>
       <c r="D134" t="s">
         <v>727</v>
@@ -26658,7 +26658,7 @@
         <v>5.8100000000000001E-3</v>
       </c>
       <c r="J134" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K134" t="s">
         <v>132</v>
@@ -26705,7 +26705,7 @@
         <v>262</v>
       </c>
       <c r="C135" t="s">
-        <v>1357</v>
+        <v>1386</v>
       </c>
       <c r="D135" t="s">
         <v>714</v>
@@ -26723,7 +26723,7 @@
         <v>6.1079999999999997E-3</v>
       </c>
       <c r="J135" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K135" t="s">
         <v>133</v>
@@ -26770,7 +26770,7 @@
         <v>240</v>
       </c>
       <c r="C136" t="s">
-        <v>1358</v>
+        <v>1387</v>
       </c>
       <c r="D136" t="s">
         <v>706</v>
@@ -26788,7 +26788,7 @@
         <v>6.7660000000000003E-3</v>
       </c>
       <c r="J136" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K136" t="s">
         <v>134</v>
@@ -26835,7 +26835,7 @@
         <v>284</v>
       </c>
       <c r="C137" t="s">
-        <v>1359</v>
+        <v>1388</v>
       </c>
       <c r="D137" t="s">
         <v>652</v>
@@ -26853,7 +26853,7 @@
         <v>6.4700000000000001E-3</v>
       </c>
       <c r="J137" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K137" t="s">
         <v>135</v>
@@ -26900,7 +26900,7 @@
         <v>276</v>
       </c>
       <c r="C138" t="s">
-        <v>1360</v>
+        <v>1389</v>
       </c>
       <c r="D138" t="s">
         <v>673</v>
@@ -26918,7 +26918,7 @@
         <v>6.8580000000000004E-3</v>
       </c>
       <c r="J138" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K138" t="s">
         <v>136</v>
@@ -26965,7 +26965,7 @@
         <v>272</v>
       </c>
       <c r="C139" t="s">
-        <v>1361</v>
+        <v>1390</v>
       </c>
       <c r="D139" t="s">
         <v>684</v>
@@ -26983,7 +26983,7 @@
         <v>6.5579999999999996E-3</v>
       </c>
       <c r="J139" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K139" t="s">
         <v>137</v>
@@ -27030,7 +27030,7 @@
         <v>296</v>
       </c>
       <c r="C140" t="s">
-        <v>1362</v>
+        <v>1391</v>
       </c>
       <c r="D140" t="s">
         <v>626</v>
@@ -27048,7 +27048,7 @@
         <v>7.4460000000000004E-3</v>
       </c>
       <c r="J140" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="K140" t="s">
         <v>138</v>
@@ -28879,7 +28879,7 @@
         <v>437</v>
       </c>
       <c r="C169" t="s">
-        <v>1363</v>
+        <v>1296</v>
       </c>
       <c r="D169" t="s">
         <v>840</v>
@@ -28944,7 +28944,7 @@
         <v>438</v>
       </c>
       <c r="C170" t="s">
-        <v>1364</v>
+        <v>1297</v>
       </c>
       <c r="D170" t="s">
         <v>850</v>
@@ -29009,7 +29009,7 @@
         <v>439</v>
       </c>
       <c r="C171" t="s">
-        <v>1365</v>
+        <v>1298</v>
       </c>
       <c r="D171" t="s">
         <v>854</v>
@@ -29074,7 +29074,7 @@
         <v>440</v>
       </c>
       <c r="C172" t="s">
-        <v>1366</v>
+        <v>1299</v>
       </c>
       <c r="D172" t="s">
         <v>838</v>
@@ -29139,7 +29139,7 @@
         <v>441</v>
       </c>
       <c r="C173" t="s">
-        <v>1367</v>
+        <v>1300</v>
       </c>
       <c r="D173" t="s">
         <v>846</v>
@@ -29204,7 +29204,7 @@
         <v>442</v>
       </c>
       <c r="C174" t="s">
-        <v>1368</v>
+        <v>1301</v>
       </c>
       <c r="D174" t="s">
         <v>836</v>
@@ -29269,7 +29269,7 @@
         <v>443</v>
       </c>
       <c r="C175" t="s">
-        <v>1369</v>
+        <v>1302</v>
       </c>
       <c r="D175" t="s">
         <v>834</v>
@@ -29334,7 +29334,7 @@
         <v>444</v>
       </c>
       <c r="C176" t="s">
-        <v>1370</v>
+        <v>1303</v>
       </c>
       <c r="D176" t="s">
         <v>860</v>
@@ -29399,7 +29399,7 @@
         <v>445</v>
       </c>
       <c r="C177" t="s">
-        <v>1371</v>
+        <v>1304</v>
       </c>
       <c r="D177" t="s">
         <v>830</v>
@@ -29464,7 +29464,7 @@
         <v>446</v>
       </c>
       <c r="C178" t="s">
-        <v>1372</v>
+        <v>1305</v>
       </c>
       <c r="D178" t="s">
         <v>842</v>
@@ -29529,7 +29529,7 @@
         <v>447</v>
       </c>
       <c r="C179" t="s">
-        <v>1373</v>
+        <v>1306</v>
       </c>
       <c r="D179" t="s">
         <v>858</v>
@@ -29594,7 +29594,7 @@
         <v>448</v>
       </c>
       <c r="C180" t="s">
-        <v>1374</v>
+        <v>1307</v>
       </c>
       <c r="D180" t="s">
         <v>864</v>
@@ -29659,7 +29659,7 @@
         <v>449</v>
       </c>
       <c r="C181" t="s">
-        <v>1375</v>
+        <v>1308</v>
       </c>
       <c r="D181" t="s">
         <v>832</v>
@@ -29724,7 +29724,7 @@
         <v>450</v>
       </c>
       <c r="C182" t="s">
-        <v>1376</v>
+        <v>1309</v>
       </c>
       <c r="D182" t="s">
         <v>828</v>
@@ -29789,7 +29789,7 @@
         <v>451</v>
       </c>
       <c r="C183" t="s">
-        <v>1377</v>
+        <v>1310</v>
       </c>
       <c r="D183" t="s">
         <v>862</v>
@@ -29854,7 +29854,7 @@
         <v>452</v>
       </c>
       <c r="C184" t="s">
-        <v>1378</v>
+        <v>1311</v>
       </c>
       <c r="D184" t="s">
         <v>866</v>
@@ -29919,7 +29919,7 @@
         <v>453</v>
       </c>
       <c r="C185" t="s">
-        <v>1379</v>
+        <v>1312</v>
       </c>
       <c r="D185" t="s">
         <v>844</v>
@@ -29984,7 +29984,7 @@
         <v>454</v>
       </c>
       <c r="C186" t="s">
-        <v>1380</v>
+        <v>1313</v>
       </c>
       <c r="D186" t="s">
         <v>848</v>
@@ -30049,7 +30049,7 @@
         <v>455</v>
       </c>
       <c r="C187" t="s">
-        <v>1381</v>
+        <v>1314</v>
       </c>
       <c r="D187" t="s">
         <v>856</v>
@@ -30114,7 +30114,7 @@
         <v>456</v>
       </c>
       <c r="C188" t="s">
-        <v>1382</v>
+        <v>1315</v>
       </c>
       <c r="D188" t="s">
         <v>852</v>
@@ -30219,19 +30219,19 @@
       </c>
       <c r="I1" s="22"/>
       <c r="K1" t="s">
-        <v>1388</v>
+        <v>1321</v>
       </c>
       <c r="L1" t="s">
-        <v>1386</v>
+        <v>1319</v>
       </c>
       <c r="M1" t="s">
-        <v>1385</v>
+        <v>1318</v>
       </c>
       <c r="N1" t="s">
-        <v>1384</v>
+        <v>1317</v>
       </c>
       <c r="O1" t="s">
-        <v>1387</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -30615,10 +30615,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>1389</v>
+        <v>1322</v>
       </c>
       <c r="B1" t="s">
-        <v>1390</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -30881,19 +30881,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>1388</v>
+        <v>1321</v>
       </c>
       <c r="B1" t="s">
-        <v>1386</v>
+        <v>1319</v>
       </c>
       <c r="C1" t="s">
-        <v>1385</v>
+        <v>1318</v>
       </c>
       <c r="D1" t="s">
-        <v>1384</v>
+        <v>1317</v>
       </c>
       <c r="E1" t="s">
-        <v>1387</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
